--- a/output/yearly_population_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_98_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5054</v>
+        <v>6731</v>
       </c>
       <c r="C2" t="n">
-        <v>4391</v>
+        <v>7708</v>
       </c>
       <c r="D2" t="n">
-        <v>32874</v>
+        <v>28040</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3375</v>
+        <v>3642</v>
       </c>
       <c r="C3" t="n">
-        <v>5109</v>
+        <v>3923</v>
       </c>
       <c r="D3" t="n">
-        <v>17013</v>
+        <v>16927</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2736</v>
+        <v>2569</v>
       </c>
       <c r="C4" t="n">
-        <v>4422</v>
+        <v>3938</v>
       </c>
       <c r="D4" t="n">
-        <v>6917</v>
+        <v>9084</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1744</v>
+        <v>1734</v>
       </c>
       <c r="C5" t="n">
-        <v>3901</v>
+        <v>4091</v>
       </c>
       <c r="D5" t="n">
-        <v>2435</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>948</v>
+        <v>1089</v>
       </c>
       <c r="C6" t="n">
-        <v>3430</v>
+        <v>3023</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>542</v>
       </c>
       <c r="C7" t="n">
-        <v>2395</v>
+        <v>1917</v>
       </c>
       <c r="D7" t="n">
-        <v>635</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>209</v>
       </c>
       <c r="C8" t="n">
-        <v>1271</v>
+        <v>944</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>406</v>
       </c>
       <c r="D9" t="n">
         <v>306</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6791</v>
+        <v>8948</v>
       </c>
       <c r="C2" t="n">
-        <v>11906</v>
+        <v>12551</v>
       </c>
       <c r="D2" t="n">
-        <v>34385</v>
+        <v>35995</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3354</v>
+        <v>4038</v>
       </c>
       <c r="C3" t="n">
-        <v>4222</v>
+        <v>4942</v>
       </c>
       <c r="D3" t="n">
-        <v>18026</v>
+        <v>17300</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2600</v>
+        <v>2585</v>
       </c>
       <c r="C4" t="n">
-        <v>4653</v>
+        <v>3811</v>
       </c>
       <c r="D4" t="n">
-        <v>8354</v>
+        <v>10087</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1908</v>
+        <v>1868</v>
       </c>
       <c r="C5" t="n">
-        <v>4017</v>
+        <v>3935</v>
       </c>
       <c r="D5" t="n">
-        <v>3026</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1164</v>
+        <v>1242</v>
       </c>
       <c r="C6" t="n">
-        <v>3605</v>
+        <v>3435</v>
       </c>
       <c r="D6" t="n">
-        <v>1270</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>574</v>
+        <v>692</v>
       </c>
       <c r="C7" t="n">
-        <v>2816</v>
+        <v>2403</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="C8" t="n">
-        <v>1731</v>
+        <v>1344</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>816</v>
+        <v>627</v>
       </c>
       <c r="D9" t="n">
         <v>316</v>
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>334</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8126</v>
+        <v>10820</v>
       </c>
       <c r="C2" t="n">
-        <v>14886</v>
+        <v>12828</v>
       </c>
       <c r="D2" t="n">
-        <v>43633</v>
+        <v>38778</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3810</v>
+        <v>4816</v>
       </c>
       <c r="C3" t="n">
-        <v>6555</v>
+        <v>7127</v>
       </c>
       <c r="D3" t="n">
-        <v>18835</v>
+        <v>18436</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2475</v>
+        <v>2682</v>
       </c>
       <c r="C4" t="n">
-        <v>4329</v>
+        <v>4183</v>
       </c>
       <c r="D4" t="n">
-        <v>9412</v>
+        <v>10722</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1943</v>
+        <v>1914</v>
       </c>
       <c r="C5" t="n">
-        <v>4157</v>
+        <v>3800</v>
       </c>
       <c r="D5" t="n">
-        <v>3701</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1326</v>
+        <v>1361</v>
       </c>
       <c r="C6" t="n">
-        <v>3739</v>
+        <v>3572</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>726</v>
+        <v>818</v>
       </c>
       <c r="C7" t="n">
-        <v>3096</v>
+        <v>2793</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>405</v>
       </c>
       <c r="C8" t="n">
-        <v>2128</v>
+        <v>1758</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C9" t="n">
-        <v>1156</v>
+        <v>887</v>
       </c>
       <c r="D9" t="n">
         <v>330</v>
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C10" t="n">
-        <v>500</v>
+        <v>412</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
         <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7352</v>
+        <v>9731</v>
       </c>
       <c r="C2" t="n">
-        <v>10241</v>
+        <v>8825</v>
       </c>
       <c r="D2" t="n">
-        <v>35810</v>
+        <v>31907</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4510</v>
+        <v>5321</v>
       </c>
       <c r="C3" t="n">
-        <v>9788</v>
+        <v>10005</v>
       </c>
       <c r="D3" t="n">
-        <v>20068</v>
+        <v>20107</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1795</v>
+        <v>1768</v>
       </c>
       <c r="C4" t="n">
-        <v>6317</v>
+        <v>5936</v>
       </c>
       <c r="D4" t="n">
-        <v>8702</v>
+        <v>10280</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1225</v>
+        <v>1257</v>
       </c>
       <c r="C5" t="n">
-        <v>3664</v>
+        <v>3500</v>
       </c>
       <c r="D5" t="n">
-        <v>2442</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>670</v>
+        <v>755</v>
       </c>
       <c r="C6" t="n">
-        <v>3034</v>
+        <v>2737</v>
       </c>
       <c r="D6" t="n">
-        <v>743</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>374</v>
       </c>
       <c r="C7" t="n">
-        <v>2085</v>
+        <v>1722</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="C8" t="n">
-        <v>1132</v>
+        <v>869</v>
       </c>
       <c r="D8" t="n">
         <v>323</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>403</v>
       </c>
       <c r="D9" t="n">
         <v>246</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4333</v>
+        <v>5640</v>
       </c>
       <c r="C2" t="n">
-        <v>4698</v>
+        <v>3699</v>
       </c>
       <c r="D2" t="n">
-        <v>24181</v>
+        <v>22375</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4868</v>
+        <v>6106</v>
       </c>
       <c r="C3" t="n">
-        <v>9076</v>
+        <v>8595</v>
       </c>
       <c r="D3" t="n">
-        <v>21245</v>
+        <v>20746</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>2686</v>
       </c>
       <c r="C4" t="n">
-        <v>7933</v>
+        <v>7915</v>
       </c>
       <c r="D4" t="n">
-        <v>10157</v>
+        <v>11481</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="C5" t="n">
-        <v>4833</v>
+        <v>4577</v>
       </c>
       <c r="D5" t="n">
-        <v>3219</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>787</v>
+        <v>890</v>
       </c>
       <c r="C6" t="n">
-        <v>3431</v>
+        <v>3134</v>
       </c>
       <c r="D6" t="n">
-        <v>902</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>2489</v>
+        <v>2141</v>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1452</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
         <v>332</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>529</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>164</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2184,7 +2184,7 @@
         <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4259</v>
+        <v>4996</v>
       </c>
       <c r="C2" t="n">
-        <v>7969</v>
+        <v>5295</v>
       </c>
       <c r="D2" t="n">
-        <v>23128</v>
+        <v>28058</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3902</v>
+        <v>4964</v>
       </c>
       <c r="C3" t="n">
-        <v>6273</v>
+        <v>5552</v>
       </c>
       <c r="D3" t="n">
-        <v>20216</v>
+        <v>19573</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2984</v>
+        <v>3551</v>
       </c>
       <c r="C4" t="n">
-        <v>8316</v>
+        <v>8159</v>
       </c>
       <c r="D4" t="n">
-        <v>11657</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1605</v>
+        <v>1693</v>
       </c>
       <c r="C5" t="n">
-        <v>6160</v>
+        <v>6019</v>
       </c>
       <c r="D5" t="n">
-        <v>4186</v>
+        <v>4929</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>935</v>
+        <v>1002</v>
       </c>
       <c r="C6" t="n">
-        <v>4050</v>
+        <v>3771</v>
       </c>
       <c r="D6" t="n">
-        <v>1223</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>416</v>
+        <v>496</v>
       </c>
       <c r="C7" t="n">
-        <v>2909</v>
+        <v>2558</v>
       </c>
       <c r="D7" t="n">
-        <v>552</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>1872</v>
+        <v>1545</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>868</v>
+        <v>710</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>343</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2551</v>
+        <v>3004</v>
       </c>
       <c r="C2" t="n">
-        <v>3806</v>
+        <v>2507</v>
       </c>
       <c r="D2" t="n">
-        <v>16125</v>
+        <v>19557</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3846</v>
+        <v>4798</v>
       </c>
       <c r="C3" t="n">
-        <v>6648</v>
+        <v>5307</v>
       </c>
       <c r="D3" t="n">
-        <v>20066</v>
+        <v>20017</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3285</v>
+        <v>3903</v>
       </c>
       <c r="C4" t="n">
-        <v>8294</v>
+        <v>7946</v>
       </c>
       <c r="D4" t="n">
-        <v>12641</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>1763</v>
       </c>
       <c r="C5" t="n">
-        <v>7631</v>
+        <v>7355</v>
       </c>
       <c r="D5" t="n">
-        <v>4445</v>
+        <v>5201</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>755</v>
+        <v>856</v>
       </c>
       <c r="C6" t="n">
-        <v>4868</v>
+        <v>4590</v>
       </c>
       <c r="D6" t="n">
-        <v>1201</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>3194</v>
+        <v>2724</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>1401</v>
+        <v>1165</v>
       </c>
       <c r="D8" t="n">
         <v>373</v>
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2891</v>
+        <v>3886</v>
       </c>
       <c r="C2" t="n">
-        <v>3295</v>
+        <v>5489</v>
       </c>
       <c r="D2" t="n">
-        <v>16075</v>
+        <v>18290</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2847</v>
+        <v>3454</v>
       </c>
       <c r="C3" t="n">
-        <v>4810</v>
+        <v>3581</v>
       </c>
       <c r="D3" t="n">
-        <v>18374</v>
+        <v>18801</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3064</v>
+        <v>3755</v>
       </c>
       <c r="C4" t="n">
-        <v>7363</v>
+        <v>6615</v>
       </c>
       <c r="D4" t="n">
-        <v>13397</v>
+        <v>14100</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2040</v>
+        <v>2287</v>
       </c>
       <c r="C5" t="n">
-        <v>7838</v>
+        <v>7533</v>
       </c>
       <c r="D5" t="n">
-        <v>5490</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>1090</v>
       </c>
       <c r="C6" t="n">
-        <v>6012</v>
+        <v>5735</v>
       </c>
       <c r="D6" t="n">
-        <v>1633</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>3911</v>
+        <v>3507</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2060</v>
+        <v>1737</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>577</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1989</v>
+        <v>2645</v>
       </c>
       <c r="C2" t="n">
-        <v>1947</v>
+        <v>2785</v>
       </c>
       <c r="D2" t="n">
-        <v>11915</v>
+        <v>13228</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2508</v>
+        <v>3148</v>
       </c>
       <c r="C3" t="n">
-        <v>3884</v>
+        <v>3926</v>
       </c>
       <c r="D3" t="n">
-        <v>17274</v>
+        <v>17897</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2739</v>
+        <v>3378</v>
       </c>
       <c r="C4" t="n">
-        <v>6417</v>
+        <v>5444</v>
       </c>
       <c r="D4" t="n">
-        <v>13739</v>
+        <v>14393</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2233</v>
+        <v>2563</v>
       </c>
       <c r="C5" t="n">
-        <v>7736</v>
+        <v>7339</v>
       </c>
       <c r="D5" t="n">
-        <v>6263</v>
+        <v>6939</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1165</v>
+        <v>1287</v>
       </c>
       <c r="C6" t="n">
-        <v>6810</v>
+        <v>6513</v>
       </c>
       <c r="D6" t="n">
-        <v>1941</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>4671</v>
+        <v>4270</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2552</v>
+        <v>2177</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>758</v>
+        <v>652</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3449</v>
+        <v>4482</v>
       </c>
       <c r="C2" t="n">
-        <v>7196</v>
+        <v>5294</v>
       </c>
       <c r="D2" t="n">
-        <v>19208</v>
+        <v>17914</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1961</v>
+        <v>2505</v>
       </c>
       <c r="C3" t="n">
-        <v>2810</v>
+        <v>3128</v>
       </c>
       <c r="D3" t="n">
-        <v>15525</v>
+        <v>16191</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2311</v>
+        <v>2867</v>
       </c>
       <c r="C4" t="n">
-        <v>5237</v>
+        <v>4651</v>
       </c>
       <c r="D4" t="n">
-        <v>13830</v>
+        <v>14460</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2214</v>
+        <v>2583</v>
       </c>
       <c r="C5" t="n">
-        <v>7055</v>
+        <v>6422</v>
       </c>
       <c r="D5" t="n">
-        <v>7077</v>
+        <v>7729</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1404</v>
+        <v>1590</v>
       </c>
       <c r="C6" t="n">
-        <v>7100</v>
+        <v>6775</v>
       </c>
       <c r="D6" t="n">
-        <v>2455</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="C7" t="n">
-        <v>5444</v>
+        <v>5145</v>
       </c>
       <c r="D7" t="n">
-        <v>837</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>3302</v>
+        <v>2894</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1320</v>
+        <v>1151</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>390</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4641</v>
+        <v>7785</v>
       </c>
       <c r="C2" t="n">
-        <v>13961</v>
+        <v>9193</v>
       </c>
       <c r="D2" t="n">
-        <v>7847</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2493</v>
+        <v>3241</v>
       </c>
       <c r="C2" t="n">
-        <v>4202</v>
+        <v>3049</v>
       </c>
       <c r="D2" t="n">
-        <v>14291</v>
+        <v>13328</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2694</v>
+        <v>3421</v>
       </c>
       <c r="C3" t="n">
-        <v>4009</v>
+        <v>3888</v>
       </c>
       <c r="D3" t="n">
-        <v>16909</v>
+        <v>17518</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3225</v>
+        <v>3853</v>
       </c>
       <c r="C4" t="n">
-        <v>7505</v>
+        <v>6799</v>
       </c>
       <c r="D4" t="n">
-        <v>14045</v>
+        <v>14764</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1338</v>
+        <v>1516</v>
       </c>
       <c r="C5" t="n">
-        <v>10173</v>
+        <v>9508</v>
       </c>
       <c r="D5" t="n">
-        <v>6322</v>
+        <v>6953</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>427</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>6657</v>
+        <v>6303</v>
       </c>
       <c r="D6" t="n">
-        <v>1892</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>3235</v>
+        <v>2836</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1293</v>
+        <v>1127</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6482</v>
+        <v>7402</v>
       </c>
       <c r="C2" t="n">
-        <v>6366</v>
+        <v>5805</v>
       </c>
       <c r="D2" t="n">
-        <v>12147</v>
+        <v>17177</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1973</v>
+        <v>3306</v>
       </c>
       <c r="C3" t="n">
-        <v>7036</v>
+        <v>4633</v>
       </c>
       <c r="D3" t="n">
-        <v>1957</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4590</v>
+        <v>5062</v>
       </c>
       <c r="C2" t="n">
-        <v>6639</v>
+        <v>5696</v>
       </c>
       <c r="D2" t="n">
-        <v>15265</v>
+        <v>30049</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3468</v>
+        <v>4400</v>
       </c>
       <c r="C3" t="n">
-        <v>5740</v>
+        <v>4567</v>
       </c>
       <c r="D3" t="n">
-        <v>3524</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>891</v>
+        <v>1470</v>
       </c>
       <c r="C4" t="n">
-        <v>4166</v>
+        <v>2757</v>
       </c>
       <c r="D4" t="n">
-        <v>1575</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4791</v>
+        <v>4811</v>
       </c>
       <c r="C2" t="n">
-        <v>6007</v>
+        <v>7148</v>
       </c>
       <c r="D2" t="n">
-        <v>28608</v>
+        <v>35510</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3306</v>
+        <v>3896</v>
       </c>
       <c r="C3" t="n">
-        <v>5447</v>
+        <v>4484</v>
       </c>
       <c r="D3" t="n">
-        <v>5148</v>
+        <v>7773</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1850</v>
+        <v>2500</v>
       </c>
       <c r="C4" t="n">
-        <v>4915</v>
+        <v>3680</v>
       </c>
       <c r="D4" t="n">
-        <v>1901</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>419</v>
+        <v>650</v>
       </c>
       <c r="C5" t="n">
-        <v>2375</v>
+        <v>1603</v>
       </c>
       <c r="D5" t="n">
-        <v>1218</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6182</v>
+        <v>5116</v>
       </c>
       <c r="C2" t="n">
-        <v>6241</v>
+        <v>6947</v>
       </c>
       <c r="D2" t="n">
-        <v>21304</v>
+        <v>40877</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>3562</v>
       </c>
       <c r="C3" t="n">
-        <v>4996</v>
+        <v>5082</v>
       </c>
       <c r="D3" t="n">
-        <v>8351</v>
+        <v>11441</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2162</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
-        <v>5046</v>
+        <v>3992</v>
       </c>
       <c r="D4" t="n">
-        <v>2435</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>929</v>
+        <v>1300</v>
       </c>
       <c r="C5" t="n">
-        <v>3642</v>
+        <v>2646</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>1334</v>
+        <v>949</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -5574,7 +5574,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6491</v>
+        <v>5617</v>
       </c>
       <c r="C2" t="n">
-        <v>4685</v>
+        <v>6508</v>
       </c>
       <c r="D2" t="n">
-        <v>29792</v>
+        <v>36870</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3375</v>
+        <v>3125</v>
       </c>
       <c r="C3" t="n">
-        <v>4607</v>
+        <v>4932</v>
       </c>
       <c r="D3" t="n">
-        <v>9156</v>
+        <v>14214</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1668</v>
+        <v>1922</v>
       </c>
       <c r="C4" t="n">
-        <v>4067</v>
+        <v>3748</v>
       </c>
       <c r="D4" t="n">
-        <v>3003</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>796</v>
+        <v>1038</v>
       </c>
       <c r="C5" t="n">
-        <v>3187</v>
+        <v>2410</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>1666</v>
+        <v>1203</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>521</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5318</v>
+        <v>5131</v>
       </c>
       <c r="C2" t="n">
-        <v>7366</v>
+        <v>3106</v>
       </c>
       <c r="D2" t="n">
-        <v>34354</v>
+        <v>26215</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4080</v>
+        <v>3614</v>
       </c>
       <c r="C3" t="n">
-        <v>3997</v>
+        <v>5027</v>
       </c>
       <c r="D3" t="n">
-        <v>11948</v>
+        <v>16974</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2205</v>
+        <v>2203</v>
       </c>
       <c r="C4" t="n">
-        <v>4308</v>
+        <v>4374</v>
       </c>
       <c r="D4" t="n">
-        <v>4123</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1085</v>
+        <v>1307</v>
       </c>
       <c r="C5" t="n">
-        <v>3636</v>
+        <v>3107</v>
       </c>
       <c r="D5" t="n">
-        <v>1497</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>495</v>
+        <v>658</v>
       </c>
       <c r="C6" t="n">
-        <v>2507</v>
+        <v>1871</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>1160</v>
+        <v>850</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4373</v>
+        <v>5471</v>
       </c>
       <c r="C2" t="n">
-        <v>6700</v>
+        <v>5538</v>
       </c>
       <c r="D2" t="n">
-        <v>37943</v>
+        <v>23361</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3849</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>5029</v>
+        <v>3468</v>
       </c>
       <c r="D3" t="n">
-        <v>14672</v>
+        <v>17230</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2664</v>
+        <v>2472</v>
       </c>
       <c r="C4" t="n">
-        <v>4045</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>5500</v>
+        <v>7758</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1546</v>
       </c>
       <c r="C5" t="n">
-        <v>3921</v>
+        <v>3693</v>
       </c>
       <c r="D5" t="n">
-        <v>1930</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>707</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>3039</v>
+        <v>2502</v>
       </c>
       <c r="D6" t="n">
-        <v>925</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="C7" t="n">
-        <v>1859</v>
+        <v>1379</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>771</v>
+        <v>585</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
         <v>297</v>
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">

--- a/output/yearly_population_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_98_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6731</v>
+        <v>5340</v>
       </c>
       <c r="C2" t="n">
-        <v>7708</v>
+        <v>12864</v>
       </c>
       <c r="D2" t="n">
-        <v>28040</v>
+        <v>21952</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>3333</v>
       </c>
       <c r="C3" t="n">
-        <v>3923</v>
+        <v>6346</v>
       </c>
       <c r="D3" t="n">
-        <v>16927</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2569</v>
+        <v>2587</v>
       </c>
       <c r="C4" t="n">
-        <v>3938</v>
+        <v>5328</v>
       </c>
       <c r="D4" t="n">
-        <v>9084</v>
+        <v>5265</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1734</v>
+        <v>1614</v>
       </c>
       <c r="C5" t="n">
-        <v>4091</v>
+        <v>4960</v>
       </c>
       <c r="D5" t="n">
-        <v>3220</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1089</v>
+        <v>930</v>
       </c>
       <c r="C6" t="n">
-        <v>3023</v>
+        <v>3906</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>439</v>
       </c>
       <c r="C7" t="n">
-        <v>1917</v>
+        <v>2485</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>944</v>
+        <v>1152</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8948</v>
+        <v>6126</v>
       </c>
       <c r="C2" t="n">
-        <v>12551</v>
+        <v>8159</v>
       </c>
       <c r="D2" t="n">
-        <v>35995</v>
+        <v>18246</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4038</v>
+        <v>3426</v>
       </c>
       <c r="C3" t="n">
-        <v>4942</v>
+        <v>8149</v>
       </c>
       <c r="D3" t="n">
-        <v>17300</v>
+        <v>11283</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2585</v>
+        <v>2486</v>
       </c>
       <c r="C4" t="n">
-        <v>3811</v>
+        <v>5644</v>
       </c>
       <c r="D4" t="n">
-        <v>10087</v>
+        <v>5945</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1868</v>
+        <v>1806</v>
       </c>
       <c r="C5" t="n">
-        <v>3935</v>
+        <v>5026</v>
       </c>
       <c r="D5" t="n">
-        <v>3991</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1242</v>
+        <v>1108</v>
       </c>
       <c r="C6" t="n">
-        <v>3435</v>
+        <v>4295</v>
       </c>
       <c r="D6" t="n">
-        <v>1460</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>692</v>
+        <v>577</v>
       </c>
       <c r="C7" t="n">
-        <v>2403</v>
+        <v>3110</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>685</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>305</v>
+        <v>243</v>
       </c>
       <c r="C8" t="n">
-        <v>1344</v>
+        <v>1701</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>627</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10820</v>
+        <v>6631</v>
       </c>
       <c r="C2" t="n">
-        <v>12828</v>
+        <v>18258</v>
       </c>
       <c r="D2" t="n">
-        <v>38778</v>
+        <v>15747</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4816</v>
+        <v>3652</v>
       </c>
       <c r="C3" t="n">
-        <v>7127</v>
+        <v>7239</v>
       </c>
       <c r="D3" t="n">
-        <v>18436</v>
+        <v>11396</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2682</v>
+        <v>2435</v>
       </c>
       <c r="C4" t="n">
-        <v>4183</v>
+        <v>6608</v>
       </c>
       <c r="D4" t="n">
-        <v>10722</v>
+        <v>6475</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1914</v>
+        <v>1847</v>
       </c>
       <c r="C5" t="n">
-        <v>3800</v>
+        <v>5128</v>
       </c>
       <c r="D5" t="n">
-        <v>4747</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1361</v>
+        <v>1259</v>
       </c>
       <c r="C6" t="n">
-        <v>3572</v>
+        <v>4509</v>
       </c>
       <c r="D6" t="n">
-        <v>1766</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>818</v>
+        <v>705</v>
       </c>
       <c r="C7" t="n">
-        <v>2793</v>
+        <v>3584</v>
       </c>
       <c r="D7" t="n">
-        <v>807</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>405</v>
+        <v>330</v>
       </c>
       <c r="C8" t="n">
-        <v>1758</v>
+        <v>2222</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="C9" t="n">
-        <v>887</v>
+        <v>1085</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>412</v>
+        <v>458</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9731</v>
+        <v>6120</v>
       </c>
       <c r="C2" t="n">
-        <v>8825</v>
+        <v>12561</v>
       </c>
       <c r="D2" t="n">
-        <v>31907</v>
+        <v>13144</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5321</v>
+        <v>4377</v>
       </c>
       <c r="C3" t="n">
-        <v>10005</v>
+        <v>11722</v>
       </c>
       <c r="D3" t="n">
-        <v>20107</v>
+        <v>12382</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1768</v>
+        <v>1706</v>
       </c>
       <c r="C4" t="n">
-        <v>5936</v>
+        <v>8538</v>
       </c>
       <c r="D4" t="n">
-        <v>10280</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1163</v>
       </c>
       <c r="C5" t="n">
-        <v>3500</v>
+        <v>4418</v>
       </c>
       <c r="D5" t="n">
-        <v>3006</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>755</v>
+        <v>651</v>
       </c>
       <c r="C6" t="n">
-        <v>2737</v>
+        <v>3512</v>
       </c>
       <c r="D6" t="n">
-        <v>790</v>
+        <v>732</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>1722</v>
+        <v>2177</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>869</v>
+        <v>1063</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5640</v>
+        <v>3770</v>
       </c>
       <c r="C2" t="n">
-        <v>3699</v>
+        <v>5533</v>
       </c>
       <c r="D2" t="n">
-        <v>22375</v>
+        <v>9005</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6106</v>
+        <v>4419</v>
       </c>
       <c r="C3" t="n">
-        <v>8595</v>
+        <v>10976</v>
       </c>
       <c r="D3" t="n">
-        <v>20746</v>
+        <v>11891</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>2358</v>
       </c>
       <c r="C4" t="n">
-        <v>7915</v>
+        <v>10155</v>
       </c>
       <c r="D4" t="n">
-        <v>11481</v>
+        <v>7023</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1371</v>
+        <v>1298</v>
       </c>
       <c r="C5" t="n">
-        <v>4577</v>
+        <v>6199</v>
       </c>
       <c r="D5" t="n">
-        <v>3880</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>890</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>3134</v>
+        <v>3996</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>2141</v>
+        <v>2721</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>1386</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>449</v>
+        <v>497</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4996</v>
+        <v>3857</v>
       </c>
       <c r="C2" t="n">
-        <v>5295</v>
+        <v>6167</v>
       </c>
       <c r="D2" t="n">
-        <v>28058</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4964</v>
+        <v>3488</v>
       </c>
       <c r="C3" t="n">
-        <v>5552</v>
+        <v>7420</v>
       </c>
       <c r="D3" t="n">
-        <v>19573</v>
+        <v>10699</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3551</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>8159</v>
+        <v>10443</v>
       </c>
       <c r="D4" t="n">
-        <v>12644</v>
+        <v>7603</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1693</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>6019</v>
+        <v>7892</v>
       </c>
       <c r="D5" t="n">
-        <v>4929</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1002</v>
+        <v>906</v>
       </c>
       <c r="C6" t="n">
-        <v>3771</v>
+        <v>4969</v>
       </c>
       <c r="D6" t="n">
-        <v>1415</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>496</v>
+        <v>417</v>
       </c>
       <c r="C7" t="n">
-        <v>2558</v>
+        <v>3257</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1545</v>
+        <v>1935</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>710</v>
+        <v>837</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3004</v>
+        <v>2307</v>
       </c>
       <c r="C2" t="n">
-        <v>2507</v>
+        <v>2968</v>
       </c>
       <c r="D2" t="n">
-        <v>19557</v>
+        <v>7523</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4798</v>
+        <v>3449</v>
       </c>
       <c r="C3" t="n">
-        <v>5307</v>
+        <v>6795</v>
       </c>
       <c r="D3" t="n">
-        <v>20017</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3903</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="n">
-        <v>7946</v>
+        <v>10270</v>
       </c>
       <c r="D4" t="n">
-        <v>13512</v>
+        <v>8035</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1763</v>
+        <v>1603</v>
       </c>
       <c r="C5" t="n">
-        <v>7355</v>
+        <v>9594</v>
       </c>
       <c r="D5" t="n">
-        <v>5201</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>745</v>
       </c>
       <c r="C6" t="n">
-        <v>4590</v>
+        <v>6009</v>
       </c>
       <c r="D6" t="n">
-        <v>1376</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2724</v>
+        <v>3465</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1165</v>
+        <v>1389</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3886</v>
+        <v>3095</v>
       </c>
       <c r="C2" t="n">
-        <v>5489</v>
+        <v>11349</v>
       </c>
       <c r="D2" t="n">
-        <v>18290</v>
+        <v>7287</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3454</v>
+        <v>2530</v>
       </c>
       <c r="C3" t="n">
-        <v>3581</v>
+        <v>4490</v>
       </c>
       <c r="D3" t="n">
-        <v>18801</v>
+        <v>9462</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3755</v>
+        <v>2841</v>
       </c>
       <c r="C4" t="n">
-        <v>6615</v>
+        <v>8520</v>
       </c>
       <c r="D4" t="n">
-        <v>14100</v>
+        <v>8163</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2287</v>
+        <v>1934</v>
       </c>
       <c r="C5" t="n">
-        <v>7533</v>
+        <v>9785</v>
       </c>
       <c r="D5" t="n">
-        <v>6239</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1090</v>
+        <v>968</v>
       </c>
       <c r="C6" t="n">
-        <v>5735</v>
+        <v>7493</v>
       </c>
       <c r="D6" t="n">
-        <v>1872</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="C7" t="n">
-        <v>3507</v>
+        <v>4528</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1737</v>
+        <v>2148</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>660</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2645</v>
+        <v>2009</v>
       </c>
       <c r="C2" t="n">
-        <v>2785</v>
+        <v>5654</v>
       </c>
       <c r="D2" t="n">
-        <v>13228</v>
+        <v>5803</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3148</v>
+        <v>2372</v>
       </c>
       <c r="C3" t="n">
-        <v>3926</v>
+        <v>6537</v>
       </c>
       <c r="D3" t="n">
-        <v>17897</v>
+        <v>8777</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3378</v>
+        <v>2513</v>
       </c>
       <c r="C4" t="n">
-        <v>5444</v>
+        <v>6920</v>
       </c>
       <c r="D4" t="n">
-        <v>14393</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2563</v>
+        <v>2105</v>
       </c>
       <c r="C5" t="n">
-        <v>7339</v>
+        <v>9507</v>
       </c>
       <c r="D5" t="n">
-        <v>6939</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>1131</v>
       </c>
       <c r="C6" t="n">
-        <v>6513</v>
+        <v>8492</v>
       </c>
       <c r="D6" t="n">
-        <v>2281</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>4270</v>
+        <v>5534</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2177</v>
+        <v>2718</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>749</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4482</v>
+        <v>2869</v>
       </c>
       <c r="C2" t="n">
-        <v>5294</v>
+        <v>5201</v>
       </c>
       <c r="D2" t="n">
-        <v>17914</v>
+        <v>10499</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2505</v>
+        <v>1892</v>
       </c>
       <c r="C3" t="n">
-        <v>3128</v>
+        <v>5522</v>
       </c>
       <c r="D3" t="n">
-        <v>16191</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2867</v>
+        <v>2141</v>
       </c>
       <c r="C4" t="n">
-        <v>4651</v>
+        <v>6617</v>
       </c>
       <c r="D4" t="n">
-        <v>14460</v>
+        <v>7912</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2583</v>
+        <v>2068</v>
       </c>
       <c r="C5" t="n">
-        <v>6422</v>
+        <v>8291</v>
       </c>
       <c r="D5" t="n">
-        <v>7729</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1590</v>
+        <v>1346</v>
       </c>
       <c r="C6" t="n">
-        <v>6775</v>
+        <v>8802</v>
       </c>
       <c r="D6" t="n">
-        <v>2833</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>454</v>
       </c>
       <c r="C7" t="n">
-        <v>5145</v>
+        <v>6604</v>
       </c>
       <c r="D7" t="n">
-        <v>932</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>2894</v>
+        <v>3709</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1151</v>
+        <v>1373</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7785</v>
+        <v>4722</v>
       </c>
       <c r="C2" t="n">
-        <v>9193</v>
+        <v>9367</v>
       </c>
       <c r="D2" t="n">
-        <v>3854</v>
+        <v>6596</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3241</v>
+        <v>2074</v>
       </c>
       <c r="C2" t="n">
-        <v>3049</v>
+        <v>3038</v>
       </c>
       <c r="D2" t="n">
-        <v>13328</v>
+        <v>7811</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3421</v>
+        <v>2552</v>
       </c>
       <c r="C3" t="n">
-        <v>3888</v>
+        <v>5947</v>
       </c>
       <c r="D3" t="n">
-        <v>17518</v>
+        <v>8743</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3853</v>
+        <v>2985</v>
       </c>
       <c r="C4" t="n">
-        <v>6799</v>
+        <v>9535</v>
       </c>
       <c r="D4" t="n">
-        <v>14764</v>
+        <v>8191</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1516</v>
+        <v>1281</v>
       </c>
       <c r="C5" t="n">
-        <v>9508</v>
+        <v>12240</v>
       </c>
       <c r="D5" t="n">
-        <v>6953</v>
+        <v>4360</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>6303</v>
+        <v>8110</v>
       </c>
       <c r="D6" t="n">
-        <v>2182</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>2836</v>
+        <v>3634</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1127</v>
+        <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7402</v>
+        <v>6461</v>
       </c>
       <c r="C2" t="n">
-        <v>5805</v>
+        <v>9789</v>
       </c>
       <c r="D2" t="n">
-        <v>17177</v>
+        <v>12465</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3306</v>
+        <v>2007</v>
       </c>
       <c r="C3" t="n">
-        <v>4633</v>
+        <v>4720</v>
       </c>
       <c r="D3" t="n">
-        <v>1286</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5062</v>
+        <v>4712</v>
       </c>
       <c r="C2" t="n">
-        <v>5696</v>
+        <v>9105</v>
       </c>
       <c r="D2" t="n">
-        <v>30049</v>
+        <v>15824</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4400</v>
+        <v>3473</v>
       </c>
       <c r="C3" t="n">
-        <v>4567</v>
+        <v>6544</v>
       </c>
       <c r="D3" t="n">
-        <v>3861</v>
+        <v>3419</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1470</v>
+        <v>906</v>
       </c>
       <c r="C4" t="n">
-        <v>2757</v>
+        <v>2808</v>
       </c>
       <c r="D4" t="n">
-        <v>1440</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="5">
@@ -4871,7 +4871,7 @@
         <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4811</v>
+        <v>4596</v>
       </c>
       <c r="C2" t="n">
-        <v>7148</v>
+        <v>5750</v>
       </c>
       <c r="D2" t="n">
-        <v>35510</v>
+        <v>17673</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3896</v>
+        <v>3356</v>
       </c>
       <c r="C3" t="n">
-        <v>4484</v>
+        <v>6873</v>
       </c>
       <c r="D3" t="n">
-        <v>7773</v>
+        <v>5157</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2500</v>
+        <v>1859</v>
       </c>
       <c r="C4" t="n">
-        <v>3680</v>
+        <v>4865</v>
       </c>
       <c r="D4" t="n">
-        <v>1861</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>650</v>
+        <v>424</v>
       </c>
       <c r="C5" t="n">
-        <v>1603</v>
+        <v>1631</v>
       </c>
       <c r="D5" t="n">
-        <v>1194</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="6">
@@ -5196,7 +5196,7 @@
         <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -5221,7 +5221,7 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>456</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5116</v>
+        <v>5075</v>
       </c>
       <c r="C2" t="n">
-        <v>6947</v>
+        <v>8807</v>
       </c>
       <c r="D2" t="n">
-        <v>40877</v>
+        <v>14893</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3562</v>
+        <v>3272</v>
       </c>
       <c r="C3" t="n">
-        <v>5082</v>
+        <v>5479</v>
       </c>
       <c r="D3" t="n">
-        <v>11441</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>2186</v>
       </c>
       <c r="C4" t="n">
-        <v>3992</v>
+        <v>5843</v>
       </c>
       <c r="D4" t="n">
-        <v>2882</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1300</v>
+        <v>932</v>
       </c>
       <c r="C5" t="n">
-        <v>2646</v>
+        <v>3273</v>
       </c>
       <c r="D5" t="n">
-        <v>1261</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>337</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
         <v>381</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5617</v>
+        <v>5439</v>
       </c>
       <c r="C2" t="n">
-        <v>6508</v>
+        <v>7937</v>
       </c>
       <c r="D2" t="n">
-        <v>36870</v>
+        <v>23872</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3125</v>
+        <v>3015</v>
       </c>
       <c r="C3" t="n">
-        <v>4932</v>
+        <v>5881</v>
       </c>
       <c r="D3" t="n">
-        <v>14214</v>
+        <v>7028</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1922</v>
+        <v>1695</v>
       </c>
       <c r="C4" t="n">
-        <v>3748</v>
+        <v>4621</v>
       </c>
       <c r="D4" t="n">
-        <v>3804</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1038</v>
+        <v>803</v>
       </c>
       <c r="C5" t="n">
-        <v>2410</v>
+        <v>3364</v>
       </c>
       <c r="D5" t="n">
-        <v>1207</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>385</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>1203</v>
+        <v>1409</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5131</v>
+        <v>5543</v>
       </c>
       <c r="C2" t="n">
-        <v>3106</v>
+        <v>6084</v>
       </c>
       <c r="D2" t="n">
-        <v>26215</v>
+        <v>17695</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3614</v>
+        <v>3539</v>
       </c>
       <c r="C3" t="n">
-        <v>5027</v>
+        <v>6089</v>
       </c>
       <c r="D3" t="n">
-        <v>16974</v>
+        <v>9340</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2203</v>
+        <v>2043</v>
       </c>
       <c r="C4" t="n">
-        <v>4374</v>
+        <v>5286</v>
       </c>
       <c r="D4" t="n">
-        <v>5787</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1307</v>
+        <v>1114</v>
       </c>
       <c r="C5" t="n">
-        <v>3107</v>
+        <v>4030</v>
       </c>
       <c r="D5" t="n">
-        <v>1657</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>658</v>
+        <v>496</v>
       </c>
       <c r="C6" t="n">
-        <v>1871</v>
+        <v>2499</v>
       </c>
       <c r="D6" t="n">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>219</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>850</v>
+        <v>970</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5471</v>
+        <v>4431</v>
       </c>
       <c r="C2" t="n">
-        <v>5538</v>
+        <v>9246</v>
       </c>
       <c r="D2" t="n">
-        <v>23361</v>
+        <v>17634</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>3710</v>
       </c>
       <c r="C3" t="n">
-        <v>3468</v>
+        <v>5326</v>
       </c>
       <c r="D3" t="n">
-        <v>17230</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2472</v>
+        <v>2399</v>
       </c>
       <c r="C4" t="n">
-        <v>4646</v>
+        <v>5572</v>
       </c>
       <c r="D4" t="n">
-        <v>7758</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1546</v>
+        <v>1373</v>
       </c>
       <c r="C5" t="n">
-        <v>3693</v>
+        <v>4633</v>
       </c>
       <c r="D5" t="n">
-        <v>2359</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>730</v>
       </c>
       <c r="C6" t="n">
-        <v>2502</v>
+        <v>3278</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>1379</v>
+        <v>1754</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>585</v>
+        <v>652</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>

--- a/output/yearly_population_iteration_98_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_98_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5340</v>
+        <v>1019</v>
       </c>
       <c r="C2" t="n">
-        <v>12864</v>
+        <v>2288</v>
       </c>
       <c r="D2" t="n">
-        <v>21952</v>
+        <v>11910</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>1823</v>
       </c>
       <c r="C3" t="n">
-        <v>6346</v>
+        <v>5811</v>
       </c>
       <c r="D3" t="n">
-        <v>10414</v>
+        <v>11283</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2587</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="n">
-        <v>5328</v>
+        <v>8241</v>
       </c>
       <c r="D4" t="n">
-        <v>5265</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1614</v>
+        <v>494</v>
       </c>
       <c r="C5" t="n">
-        <v>4960</v>
+        <v>4999</v>
       </c>
       <c r="D5" t="n">
-        <v>2162</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>930</v>
+        <v>216</v>
       </c>
       <c r="C6" t="n">
-        <v>3906</v>
+        <v>1938</v>
       </c>
       <c r="D6" t="n">
-        <v>1032</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>2485</v>
+        <v>721</v>
       </c>
       <c r="D7" t="n">
-        <v>641</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1152</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6126</v>
+        <v>1366</v>
       </c>
       <c r="C2" t="n">
-        <v>8159</v>
+        <v>7629</v>
       </c>
       <c r="D2" t="n">
-        <v>18246</v>
+        <v>22158</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3426</v>
+        <v>1214</v>
       </c>
       <c r="C3" t="n">
-        <v>8149</v>
+        <v>3404</v>
       </c>
       <c r="D3" t="n">
-        <v>11283</v>
+        <v>10679</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2486</v>
+        <v>1291</v>
       </c>
       <c r="C4" t="n">
-        <v>5644</v>
+        <v>6795</v>
       </c>
       <c r="D4" t="n">
-        <v>5945</v>
+        <v>6086</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1806</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
-        <v>5026</v>
+        <v>6606</v>
       </c>
       <c r="D5" t="n">
-        <v>2552</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>4295</v>
+        <v>3493</v>
       </c>
       <c r="D6" t="n">
-        <v>1191</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>577</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>3110</v>
+        <v>1324</v>
       </c>
       <c r="D7" t="n">
-        <v>685</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1701</v>
+        <v>529</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6631</v>
+        <v>711</v>
       </c>
       <c r="C2" t="n">
-        <v>18258</v>
+        <v>3193</v>
       </c>
       <c r="D2" t="n">
-        <v>15747</v>
+        <v>14933</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3652</v>
+        <v>1209</v>
       </c>
       <c r="C3" t="n">
-        <v>7239</v>
+        <v>4918</v>
       </c>
       <c r="D3" t="n">
-        <v>11396</v>
+        <v>11857</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2435</v>
+        <v>1405</v>
       </c>
       <c r="C4" t="n">
-        <v>6608</v>
+        <v>5971</v>
       </c>
       <c r="D4" t="n">
-        <v>6475</v>
+        <v>6722</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1847</v>
+        <v>704</v>
       </c>
       <c r="C5" t="n">
-        <v>5128</v>
+        <v>7472</v>
       </c>
       <c r="D5" t="n">
-        <v>2963</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1259</v>
+        <v>265</v>
       </c>
       <c r="C6" t="n">
-        <v>4509</v>
+        <v>4534</v>
       </c>
       <c r="D6" t="n">
-        <v>1346</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>705</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3584</v>
+        <v>1273</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2222</v>
+        <v>504</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1085</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>458</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6120</v>
+        <v>533</v>
       </c>
       <c r="C2" t="n">
-        <v>12561</v>
+        <v>5038</v>
       </c>
       <c r="D2" t="n">
-        <v>13144</v>
+        <v>13545</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4377</v>
+        <v>838</v>
       </c>
       <c r="C3" t="n">
-        <v>11722</v>
+        <v>3533</v>
       </c>
       <c r="D3" t="n">
-        <v>12382</v>
+        <v>11489</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>1159</v>
       </c>
       <c r="C4" t="n">
-        <v>8538</v>
+        <v>5338</v>
       </c>
       <c r="D4" t="n">
-        <v>6274</v>
+        <v>7518</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1163</v>
+        <v>907</v>
       </c>
       <c r="C5" t="n">
-        <v>4418</v>
+        <v>6696</v>
       </c>
       <c r="D5" t="n">
-        <v>2115</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>651</v>
+        <v>403</v>
       </c>
       <c r="C6" t="n">
-        <v>3512</v>
+        <v>5914</v>
       </c>
       <c r="D6" t="n">
-        <v>732</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2177</v>
+        <v>2767</v>
       </c>
       <c r="D7" t="n">
-        <v>463</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>835</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>448</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3770</v>
+        <v>342</v>
       </c>
       <c r="C2" t="n">
-        <v>5533</v>
+        <v>3702</v>
       </c>
       <c r="D2" t="n">
-        <v>9005</v>
+        <v>9833</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4419</v>
+        <v>631</v>
       </c>
       <c r="C3" t="n">
-        <v>10976</v>
+        <v>3785</v>
       </c>
       <c r="D3" t="n">
-        <v>11891</v>
+        <v>11106</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2358</v>
+        <v>968</v>
       </c>
       <c r="C4" t="n">
-        <v>10155</v>
+        <v>4531</v>
       </c>
       <c r="D4" t="n">
-        <v>7023</v>
+        <v>7971</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1298</v>
+        <v>963</v>
       </c>
       <c r="C5" t="n">
-        <v>6199</v>
+        <v>6240</v>
       </c>
       <c r="D5" t="n">
-        <v>2610</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>508</v>
       </c>
       <c r="C6" t="n">
-        <v>3996</v>
+        <v>6441</v>
       </c>
       <c r="D6" t="n">
-        <v>877</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>2721</v>
+        <v>3938</v>
       </c>
       <c r="D7" t="n">
-        <v>509</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1386</v>
+        <v>1305</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3857</v>
+        <v>649</v>
       </c>
       <c r="C2" t="n">
-        <v>6167</v>
+        <v>4582</v>
       </c>
       <c r="D2" t="n">
-        <v>10758</v>
+        <v>12380</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3488</v>
+        <v>432</v>
       </c>
       <c r="C3" t="n">
-        <v>7420</v>
+        <v>3290</v>
       </c>
       <c r="D3" t="n">
-        <v>10699</v>
+        <v>10186</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>723</v>
       </c>
       <c r="C4" t="n">
-        <v>10443</v>
+        <v>4071</v>
       </c>
       <c r="D4" t="n">
-        <v>7603</v>
+        <v>8240</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>891</v>
       </c>
       <c r="C5" t="n">
-        <v>7892</v>
+        <v>5366</v>
       </c>
       <c r="D5" t="n">
-        <v>3208</v>
+        <v>4321</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>906</v>
+        <v>634</v>
       </c>
       <c r="C6" t="n">
-        <v>4969</v>
+        <v>6290</v>
       </c>
       <c r="D6" t="n">
-        <v>1114</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>417</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>3257</v>
+        <v>5054</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1935</v>
+        <v>2375</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>837</v>
+        <v>775</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2307</v>
+        <v>436</v>
       </c>
       <c r="C2" t="n">
-        <v>2968</v>
+        <v>2382</v>
       </c>
       <c r="D2" t="n">
-        <v>7523</v>
+        <v>8913</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3449</v>
+        <v>648</v>
       </c>
       <c r="C3" t="n">
-        <v>6795</v>
+        <v>3904</v>
       </c>
       <c r="D3" t="n">
-        <v>10465</v>
+        <v>11066</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3061</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="n">
-        <v>10270</v>
+        <v>5784</v>
       </c>
       <c r="D4" t="n">
-        <v>8035</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1603</v>
+        <v>651</v>
       </c>
       <c r="C5" t="n">
-        <v>9594</v>
+        <v>8373</v>
       </c>
       <c r="D5" t="n">
-        <v>3387</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>745</v>
+        <v>227</v>
       </c>
       <c r="C6" t="n">
-        <v>6009</v>
+        <v>6555</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3465</v>
+        <v>2327</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1389</v>
+        <v>759</v>
       </c>
       <c r="D8" t="n">
         <v>374</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3095</v>
+        <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>11349</v>
+        <v>2211</v>
       </c>
       <c r="D2" t="n">
-        <v>7287</v>
+        <v>6616</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2530</v>
+        <v>474</v>
       </c>
       <c r="C3" t="n">
-        <v>4490</v>
+        <v>2763</v>
       </c>
       <c r="D3" t="n">
-        <v>9462</v>
+        <v>9962</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2841</v>
+        <v>781</v>
       </c>
       <c r="C4" t="n">
-        <v>8520</v>
+        <v>4561</v>
       </c>
       <c r="D4" t="n">
-        <v>8163</v>
+        <v>8374</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1934</v>
+        <v>620</v>
       </c>
       <c r="C5" t="n">
-        <v>9785</v>
+        <v>6336</v>
       </c>
       <c r="D5" t="n">
-        <v>3953</v>
+        <v>4170</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>968</v>
+        <v>228</v>
       </c>
       <c r="C6" t="n">
-        <v>7493</v>
+        <v>6054</v>
       </c>
       <c r="D6" t="n">
-        <v>1399</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>4528</v>
+        <v>3037</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2148</v>
+        <v>884</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>660</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2009</v>
+        <v>292</v>
       </c>
       <c r="C2" t="n">
-        <v>5654</v>
+        <v>5549</v>
       </c>
       <c r="D2" t="n">
-        <v>5803</v>
+        <v>7977</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2372</v>
+        <v>293</v>
       </c>
       <c r="C3" t="n">
-        <v>6537</v>
+        <v>2148</v>
       </c>
       <c r="D3" t="n">
-        <v>8777</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2513</v>
+        <v>553</v>
       </c>
       <c r="C4" t="n">
-        <v>6920</v>
+        <v>3447</v>
       </c>
       <c r="D4" t="n">
-        <v>8155</v>
+        <v>8424</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2105</v>
+        <v>632</v>
       </c>
       <c r="C5" t="n">
-        <v>9507</v>
+        <v>5293</v>
       </c>
       <c r="D5" t="n">
-        <v>4315</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1131</v>
+        <v>372</v>
       </c>
       <c r="C6" t="n">
-        <v>8492</v>
+        <v>6132</v>
       </c>
       <c r="D6" t="n">
-        <v>1644</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>5534</v>
+        <v>4603</v>
       </c>
       <c r="D7" t="n">
-        <v>689</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>2718</v>
+        <v>1926</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>749</v>
+        <v>558</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2869</v>
+        <v>152</v>
       </c>
       <c r="C2" t="n">
-        <v>5201</v>
+        <v>9396</v>
       </c>
       <c r="D2" t="n">
-        <v>10499</v>
+        <v>17043</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1892</v>
+        <v>242</v>
       </c>
       <c r="C3" t="n">
-        <v>5522</v>
+        <v>3390</v>
       </c>
       <c r="D3" t="n">
-        <v>7942</v>
+        <v>8068</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2141</v>
+        <v>380</v>
       </c>
       <c r="C4" t="n">
-        <v>6617</v>
+        <v>2668</v>
       </c>
       <c r="D4" t="n">
-        <v>7912</v>
+        <v>8136</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2068</v>
+        <v>541</v>
       </c>
       <c r="C5" t="n">
-        <v>8291</v>
+        <v>4243</v>
       </c>
       <c r="D5" t="n">
-        <v>4699</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1346</v>
+        <v>451</v>
       </c>
       <c r="C6" t="n">
-        <v>8802</v>
+        <v>5656</v>
       </c>
       <c r="D6" t="n">
-        <v>1956</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>454</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>6604</v>
+        <v>5335</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>3709</v>
+        <v>3158</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1373</v>
+        <v>1161</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4722</v>
+        <v>2749</v>
       </c>
       <c r="C2" t="n">
-        <v>9367</v>
+        <v>10354</v>
       </c>
       <c r="D2" t="n">
-        <v>6596</v>
+        <v>9702</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2074</v>
+        <v>241</v>
       </c>
       <c r="C2" t="n">
-        <v>3038</v>
+        <v>8158</v>
       </c>
       <c r="D2" t="n">
-        <v>7811</v>
+        <v>17605</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2552</v>
+        <v>171</v>
       </c>
       <c r="C3" t="n">
-        <v>5947</v>
+        <v>5418</v>
       </c>
       <c r="D3" t="n">
-        <v>8743</v>
+        <v>8746</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2985</v>
+        <v>278</v>
       </c>
       <c r="C4" t="n">
-        <v>9535</v>
+        <v>2926</v>
       </c>
       <c r="D4" t="n">
-        <v>8191</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1281</v>
+        <v>439</v>
       </c>
       <c r="C5" t="n">
-        <v>12240</v>
+        <v>3428</v>
       </c>
       <c r="D5" t="n">
-        <v>4360</v>
+        <v>5513</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>419</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>8110</v>
+        <v>4977</v>
       </c>
       <c r="D6" t="n">
-        <v>1616</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>3634</v>
+        <v>5418</v>
       </c>
       <c r="D7" t="n">
-        <v>526</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>1345</v>
+        <v>4074</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>1962</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>656</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6461</v>
+        <v>3099</v>
       </c>
       <c r="C2" t="n">
-        <v>9789</v>
+        <v>6902</v>
       </c>
       <c r="D2" t="n">
-        <v>12465</v>
+        <v>14584</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2007</v>
+        <v>911</v>
       </c>
       <c r="C3" t="n">
-        <v>4720</v>
+        <v>4088</v>
       </c>
       <c r="D3" t="n">
-        <v>1747</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4712</v>
+        <v>2525</v>
       </c>
       <c r="C2" t="n">
-        <v>9105</v>
+        <v>8691</v>
       </c>
       <c r="D2" t="n">
-        <v>15824</v>
+        <v>16557</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3473</v>
+        <v>1695</v>
       </c>
       <c r="C3" t="n">
-        <v>6544</v>
+        <v>4962</v>
       </c>
       <c r="D3" t="n">
-        <v>3419</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>906</v>
+        <v>448</v>
       </c>
       <c r="C4" t="n">
-        <v>2808</v>
+        <v>2598</v>
       </c>
       <c r="D4" t="n">
-        <v>1533</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4596</v>
+        <v>2719</v>
       </c>
       <c r="C2" t="n">
-        <v>5750</v>
+        <v>4089</v>
       </c>
       <c r="D2" t="n">
-        <v>17673</v>
+        <v>18275</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>1743</v>
       </c>
       <c r="C3" t="n">
-        <v>6873</v>
+        <v>6142</v>
       </c>
       <c r="D3" t="n">
-        <v>5157</v>
+        <v>5830</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1859</v>
+        <v>941</v>
       </c>
       <c r="C4" t="n">
-        <v>4865</v>
+        <v>3973</v>
       </c>
       <c r="D4" t="n">
-        <v>1848</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>424</v>
+        <v>237</v>
       </c>
       <c r="C5" t="n">
-        <v>1631</v>
+        <v>1602</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5075</v>
+        <v>2280</v>
       </c>
       <c r="C2" t="n">
-        <v>8807</v>
+        <v>9392</v>
       </c>
       <c r="D2" t="n">
-        <v>14893</v>
+        <v>22594</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3272</v>
+        <v>1830</v>
       </c>
       <c r="C3" t="n">
-        <v>5479</v>
+        <v>4321</v>
       </c>
       <c r="D3" t="n">
-        <v>6696</v>
+        <v>7401</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2186</v>
+        <v>1159</v>
       </c>
       <c r="C4" t="n">
-        <v>5843</v>
+        <v>5139</v>
       </c>
       <c r="D4" t="n">
-        <v>2395</v>
+        <v>2630</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>932</v>
+        <v>500</v>
       </c>
       <c r="C5" t="n">
-        <v>3273</v>
+        <v>2888</v>
       </c>
       <c r="D5" t="n">
-        <v>1264</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>251</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>960</v>
+        <v>977</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5439</v>
+        <v>1950</v>
       </c>
       <c r="C2" t="n">
-        <v>7937</v>
+        <v>7994</v>
       </c>
       <c r="D2" t="n">
-        <v>23872</v>
+        <v>19328</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3015</v>
+        <v>1683</v>
       </c>
       <c r="C3" t="n">
-        <v>5881</v>
+        <v>6066</v>
       </c>
       <c r="D3" t="n">
-        <v>7028</v>
+        <v>9189</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1695</v>
+        <v>1266</v>
       </c>
       <c r="C4" t="n">
-        <v>4621</v>
+        <v>4584</v>
       </c>
       <c r="D4" t="n">
-        <v>2710</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>803</v>
+        <v>712</v>
       </c>
       <c r="C5" t="n">
-        <v>3364</v>
+        <v>4016</v>
       </c>
       <c r="D5" t="n">
-        <v>1141</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C6" t="n">
-        <v>1409</v>
+        <v>1938</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>415</v>
+        <v>634</v>
       </c>
       <c r="D7" t="n">
-        <v>516</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5543</v>
+        <v>2236</v>
       </c>
       <c r="C2" t="n">
-        <v>6084</v>
+        <v>6808</v>
       </c>
       <c r="D2" t="n">
-        <v>17695</v>
+        <v>20441</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3539</v>
+        <v>1504</v>
       </c>
       <c r="C3" t="n">
-        <v>6089</v>
+        <v>6126</v>
       </c>
       <c r="D3" t="n">
-        <v>9340</v>
+        <v>10016</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2043</v>
+        <v>1245</v>
       </c>
       <c r="C4" t="n">
-        <v>5286</v>
+        <v>5198</v>
       </c>
       <c r="D4" t="n">
-        <v>3472</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1114</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>4030</v>
+        <v>4216</v>
       </c>
       <c r="D5" t="n">
-        <v>1422</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>496</v>
+        <v>429</v>
       </c>
       <c r="C6" t="n">
-        <v>2499</v>
+        <v>2915</v>
       </c>
       <c r="D6" t="n">
-        <v>823</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>970</v>
+        <v>1247</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>446</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4431</v>
+        <v>2019</v>
       </c>
       <c r="C2" t="n">
-        <v>9246</v>
+        <v>4193</v>
       </c>
       <c r="D2" t="n">
-        <v>17634</v>
+        <v>16054</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3710</v>
+        <v>2111</v>
       </c>
       <c r="C3" t="n">
-        <v>5326</v>
+        <v>8830</v>
       </c>
       <c r="D3" t="n">
-        <v>10004</v>
+        <v>11099</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>786</v>
       </c>
       <c r="C4" t="n">
-        <v>5572</v>
+        <v>7340</v>
       </c>
       <c r="D4" t="n">
-        <v>4493</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1373</v>
+        <v>396</v>
       </c>
       <c r="C5" t="n">
-        <v>4633</v>
+        <v>2856</v>
       </c>
       <c r="D5" t="n">
-        <v>1739</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>730</v>
+        <v>161</v>
       </c>
       <c r="C6" t="n">
-        <v>3278</v>
+        <v>1222</v>
       </c>
       <c r="D6" t="n">
-        <v>920</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1754</v>
+        <v>437</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>652</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
